--- a/netlify/template-files/isms-scoping-questionnaire.xlsx
+++ b/netlify/template-files/isms-scoping-questionnaire.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISO 27001 Scoping Questionnaire" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Reference" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope Summary Tracker" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Document History" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -294,8 +295,12 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="43">
+  <fills count="44">
     <fill>
       <patternFill/>
     </fill>
@@ -546,6 +551,11 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B21B6"/>
       </patternFill>
     </fill>
   </fills>
@@ -837,7 +847,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -944,6 +954,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1464,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="B1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68181818181818" defaultRowHeight="14.5"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -7377,7 +7388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="B1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68181818181818" defaultRowHeight="14.5"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -7393,7 +7404,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="7.5" customHeight="1"/>
     <row r="4" ht="19.5" customHeight="1">
       <c r="B4" s="11" t="inlineStr">
@@ -7790,7 +7800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="B1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68181818181818" defaultRowHeight="14.5"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -8045,7 +8055,6 @@
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20" ht="19.5" customHeight="1">
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -8087,4 +8096,79 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="B1" s="38" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="38" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="38" t="inlineStr">
+        <is>
+          <t>Written by</t>
+        </is>
+      </c>
+      <c r="E1" s="38" t="inlineStr">
+        <is>
+          <t>Approved by</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[TODAYS DATE]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial Version</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[Name]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[Name]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>